--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484035_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484035_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9211</v>
+        <v>7.1709</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5034</v>
+        <v>4.1179</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4177</v>
+        <v>3.053</v>
       </c>
       <c r="G2" t="n">
         <v>0.9598</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8937</v>
+        <v>1.1435</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2528</v>
+        <v>0.8673</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6409</v>
+        <v>0.2762</v>
       </c>
       <c r="V2" t="n">
         <v>3.2821</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4825</v>
+        <v>6.3137</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8809</v>
+        <v>5.5157</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6016</v>
+        <v>0.798</v>
       </c>
       <c r="G3" t="n">
         <v>4.5633</v>
@@ -688,13 +688,13 @@
         <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6002999999999999</v>
+        <v>0.231</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2323</v>
+        <v>0.4026</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.368</v>
+        <v>-0.1716</v>
       </c>
       <c r="V3" t="n">
         <v>-0.266</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4593</v>
+        <v>3.4236</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1235</v>
+        <v>2.9194</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3359</v>
+        <v>0.5042</v>
       </c>
       <c r="G4" t="n">
         <v>0.9787</v>
@@ -766,13 +766,13 @@
         <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7096</v>
+        <v>-0.7453</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3173</v>
+        <v>-0.5214</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3923</v>
+        <v>-0.224</v>
       </c>
       <c r="V4" t="n">
         <v>1.2065</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MAÑES CARRETERO</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9778</v>
+        <v>2.6557</v>
       </c>
       <c r="E5" t="n">
-        <v>0.555</v>
+        <v>1.0423</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4228</v>
+        <v>1.6134</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3298</v>
+        <v>2.9325</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5993000000000001</v>
+        <v>1.0073</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2695</v>
+        <v>1.9252</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9736</v>
+        <v>3.7524</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8531</v>
+        <v>2.3844</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1205</v>
+        <v>1.368</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3034</v>
+        <v>-0.82</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4525</v>
+        <v>-1.3771</v>
       </c>
       <c r="O5" t="n">
-        <v>0.149</v>
+        <v>0.5572</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.579</v>
+        <v>-3.1741</v>
       </c>
       <c r="R5" t="n">
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.034</v>
+        <v>0.0524</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1813</v>
+        <v>-0.0679</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1472</v>
+        <v>0.1203</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3417</v>
+        <v>0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3417</v>
+        <v>0.532</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,75 +877,71 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7592</v>
+        <v>1.4932</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0617</v>
+        <v>0.3509</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6975</v>
+        <v>1.1423</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9325</v>
+        <v>-0.3298</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0073</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9252</v>
+        <v>0.2695</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7524</v>
+        <v>0.9736</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3844</v>
+        <v>0.8531</v>
       </c>
       <c r="L6" t="n">
-        <v>1.368</v>
+        <v>0.1205</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.82</v>
+        <v>-1.3034</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3771</v>
+        <v>-1.4525</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5572</v>
+        <v>0.149</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1741</v>
+        <v>-2.579</v>
       </c>
       <c r="R6" t="n">
         <v>2.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.844</v>
+        <v>-0.5187</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0485</v>
+        <v>-0.3853</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2045</v>
+        <v>-0.1333</v>
       </c>
       <c r="V6" t="n">
-        <v>0.266</v>
+        <v>2.3417</v>
       </c>
       <c r="W6" t="n">
-        <v>0.532</v>
+        <v>2.3417</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A. CRUZ URBANEJA</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -955,71 +951,75 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1723</v>
+        <v>0.735</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7062</v>
+        <v>0.0786</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5339</v>
+        <v>0.6564</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6719</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.322</v>
+        <v>-0.2729</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3499</v>
+        <v>0.3589</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3163</v>
+        <v>0.3223</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1089</v>
+        <v>0.2419</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2074</v>
+        <v>0.0803</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6444</v>
+        <v>-0.2363</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7869</v>
+        <v>-0.5148</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1425</v>
+        <v>0.2786</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3887</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1705</v>
+        <v>-0.3429</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4874</v>
+        <v>-0.2437</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6831</v>
+        <v>-0.0993</v>
       </c>
       <c r="V7" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>. VICENTE SABARIEGO</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1029,13 +1029,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0262</v>
+        <v>0.735</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2898</v>
+        <v>0.0786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2636</v>
+        <v>0.6564</v>
       </c>
       <c r="G8" t="n">
         <v>0.08599999999999999</v>
@@ -1074,13 +1074,13 @@
         <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1041</v>
+        <v>-0.3429</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6121</v>
+        <v>-0.2437</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.492</v>
+        <v>-0.0993</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1107,64 +1107,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0262</v>
+        <v>0.5789</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2898</v>
+        <v>0.9726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2636</v>
+        <v>-0.3936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08599999999999999</v>
+        <v>1.6719</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2729</v>
+        <v>0.322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3589</v>
+        <v>1.3499</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3223</v>
+        <v>2.3163</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2419</v>
+        <v>1.1089</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0803</v>
+        <v>1.2074</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2363</v>
+        <v>-0.6444</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5148</v>
+        <v>-0.7869</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2786</v>
+        <v>0.1425</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9919</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.3887</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1041</v>
+        <v>-0.7638</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6121</v>
+        <v>-0.221</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.492</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>A. RODRIGUEZ LARA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,58 +1185,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1487</v>
+        <v>-0.0216</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4838</v>
+        <v>0.0177</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3351</v>
+        <v>-0.0393</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3551</v>
+        <v>-0.2908</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1337</v>
+        <v>-0.0253</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7786</v>
+        <v>-0.2656</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.0403</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7354000000000001</v>
+        <v>0.0403</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6425999999999999</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2623</v>
+        <v>-0.3312</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3983</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.136</v>
+        <v>-0.2656</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7934</v>
+        <v>0.0709</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7912</v>
+        <v>-0.0227</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0022</v>
+        <v>0.0935</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1251,7 +1251,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LARA</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1263,19 +1263,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1797</v>
+        <v>-0.2888</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0844</v>
+        <v>-0.0447</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0954</v>
+        <v>-0.2441</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2908</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0253</v>
+        <v>-0.4285</v>
       </c>
       <c r="I11" t="n">
         <v>-0.2656</v>
@@ -1290,31 +1290,31 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3312</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.4688</v>
       </c>
       <c r="O11" t="n">
         <v>-0.2656</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0873</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1247</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0374</v>
+        <v>0.0935</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>G. RODRIGUEZ FLAQUE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1341,73 +1341,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4469</v>
+        <v>-0.3516</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1467</v>
+        <v>-1.1426</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3002</v>
+        <v>0.791</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-1.2235</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4285</v>
+        <v>-0.0859</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2656</v>
+        <v>-1.1375</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0403</v>
+        <v>-1.5167</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0403</v>
+        <v>-0.2366</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-1.2801</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7344000000000001</v>
+        <v>0.2932</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4688</v>
+        <v>0.1507</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2656</v>
+        <v>0.1425</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1496</v>
+        <v>0.5427</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.187</v>
+        <v>0.3741</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0374</v>
+        <v>0.1686</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1419,73 +1419,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5325</v>
+        <v>-1.1628</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06710000000000001</v>
+        <v>-1.4418</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5996</v>
+        <v>0.279</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3014</v>
+        <v>-0.3551</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3014</v>
+        <v>-1.1337</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.7786</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3014</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3014</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.2623</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.3983</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9919</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2332</v>
+        <v>0.7794</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3604</v>
+        <v>0.8333</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8728</v>
+        <v>-0.0539</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ FLAQUE</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1497,73 +1497,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.3347</v>
+        <v>-1.4996</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8171</v>
+        <v>-2.1108</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4824</v>
+        <v>0.6112</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2235</v>
+        <v>-1.9488</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0859</v>
+        <v>-1.139</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1375</v>
+        <v>-0.8097</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.5167</v>
+        <v>-1.2946</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2366</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2801</v>
+        <v>-0.6802</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2932</v>
+        <v>-0.6542</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1507</v>
+        <v>-0.5246</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1425</v>
+        <v>-0.1295</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.5952</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4404</v>
+        <v>-0.5427</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3004</v>
+        <v>-0.221</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.14</v>
+        <v>-0.3217</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1575,67 +1575,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.794</v>
+        <v>-1.7228</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.3772</v>
+        <v>-0.7492</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5832000000000001</v>
+        <v>-0.9737</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.9488</v>
+        <v>-0.3014</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.139</v>
+        <v>-0.3014</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8097</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2946</v>
+        <v>-0.3014</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.3014</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6542</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5246</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1295</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9919</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.5952</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8372000000000001</v>
+        <v>1.0429</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4874</v>
+        <v>0.5442</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3498</v>
+        <v>0.4988</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="16">
@@ -1653,34 +1653,34 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>16.2833</v>
+        <v>18.0588</v>
       </c>
       <c r="E16" t="n">
-        <v>8.408999999999999</v>
+        <v>9.6046</v>
       </c>
       <c r="F16" t="n">
-        <v>7.8743</v>
+        <v>8.4542</v>
       </c>
       <c r="G16" t="n">
-        <v>6.134699999999999</v>
+        <v>6.134699999999998</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9284999999999998</v>
+        <v>-0.9285</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0633</v>
+        <v>7.063300000000001</v>
       </c>
       <c r="J16" t="n">
         <v>11.3974</v>
       </c>
       <c r="K16" t="n">
-        <v>6.7507</v>
+        <v>6.750700000000001</v>
       </c>
       <c r="L16" t="n">
         <v>4.646599999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.263</v>
+        <v>-5.263000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>-7.6793</v>
@@ -1698,13 +1698,13 @@
         <v>17.8546</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.160799999999999</v>
+        <v>0.6149999999999997</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1861000000000001</v>
+        <v>1.0098</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9747999999999999</v>
+        <v>-0.3949999999999998</v>
       </c>
       <c r="V16" t="n">
         <v>5.357899999999999</v>
@@ -1731,13 +1731,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1675</v>
+        <v>5.1734</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1828</v>
+        <v>4.0808</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9847</v>
+        <v>1.0926</v>
       </c>
       <c r="G17" t="n">
         <v>1.7404</v>
@@ -1776,13 +1776,13 @@
         <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0979</v>
+        <v>1.1039</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7993</v>
+        <v>0.6973</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2986</v>
+        <v>0.4066</v>
       </c>
       <c r="V17" t="n">
         <v>0.9405</v>
@@ -1809,13 +1809,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9586</v>
+        <v>3.7485</v>
       </c>
       <c r="E18" t="n">
-        <v>3.057</v>
+        <v>3.7712</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0984</v>
+        <v>-0.0227</v>
       </c>
       <c r="G18" t="n">
         <v>2.9426</v>
@@ -1854,13 +1854,13 @@
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8452</v>
+        <v>-0.0553</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.2833</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1524</v>
+        <v>0.228</v>
       </c>
       <c r="V18" t="n">
         <v>0.266</v>
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2577</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6309</v>
+        <v>-0.2228</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6268</v>
+        <v>-0.6829</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3992</v>
@@ -1932,13 +1932,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0407</v>
+        <v>-0.6887</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8728</v>
+        <v>-0.4647</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1678</v>
+        <v>-0.224</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2065</v>
@@ -1953,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. NUÑEZ NAVARRO</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8102</v>
+        <v>-1.4261</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1373</v>
+        <v>0.2159</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3271</v>
+        <v>-1.642</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5607</v>
+        <v>2.0103</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3884</v>
+        <v>2.5856</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1723</v>
+        <v>-0.5753</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2589</v>
+        <v>2.3924</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3392</v>
+        <v>3.1102</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0803</v>
+        <v>-0.7178</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3018</v>
+        <v>-0.3821</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0492</v>
+        <v>-0.5246</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2526</v>
+        <v>0.1425</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7935</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2068</v>
+        <v>-0.2381</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1054</v>
+        <v>-0.1927</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1014</v>
+        <v>-0.0454</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3373</v>
+        <v>-1.8097</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3373</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>A. VICENTE ALONSO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,73 +2043,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9805</v>
+        <v>-1.7341</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0902</v>
+        <v>-1.849</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8903</v>
+        <v>0.115</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0103</v>
+        <v>-0.5845</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5856</v>
+        <v>-0.1517</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5753</v>
+        <v>-0.4327</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3924</v>
+        <v>1.042</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1102</v>
+        <v>0.555</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7178</v>
+        <v>0.487</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3821</v>
+        <v>-1.6265</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5246</v>
+        <v>-0.7067</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1425</v>
+        <v>-0.9198</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3887</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7924</v>
+        <v>-0.4237</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4988</v>
+        <v>-0.1813</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2937</v>
+        <v>-0.2424</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8097</v>
+        <v>0.266</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GOMES CORREIA</t>
+          <t>A. NUÑEZ NAVARRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,73 +2121,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1762</v>
+        <v>-2.0661</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7235</v>
+        <v>-2.7495</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8997</v>
+        <v>0.6834</v>
       </c>
       <c r="G22" t="n">
-        <v>0.59</v>
+        <v>-2.5607</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7793</v>
+        <v>-2.3884</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1893</v>
+        <v>-0.1723</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0951</v>
+        <v>-1.2589</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0925</v>
+        <v>-1.3392</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0026</v>
+        <v>0.0803</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5051</v>
+        <v>-1.3018</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3132</v>
+        <v>-1.0492</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1918</v>
+        <v>-0.2526</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2262</v>
+        <v>0.9508</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3797</v>
+        <v>0.4932</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1535</v>
+        <v>0.4576</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3417</v>
+        <v>0.3373</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3417</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. NEBRA SANCHEZ</t>
+          <t>A. GOMES CORREIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,73 +2199,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6616</v>
+        <v>-2.4389</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0933</v>
+        <v>0.8255</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5684</v>
+        <v>-3.2644</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2876</v>
+        <v>0.59</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8012</v>
+        <v>1.7793</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0887</v>
+        <v>-1.1893</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2205</v>
+        <v>2.0951</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9355</v>
+        <v>2.0925</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.156</v>
+        <v>0.0026</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0671</v>
+        <v>-1.5051</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1343</v>
+        <v>-0.3132</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9328</v>
+        <v>-1.1918</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0227</v>
+        <v>-0.4889</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1191</v>
+        <v>-0.2776</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0964</v>
+        <v>-0.2112</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.3417</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.3417</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. VICENTE ALONSO</t>
+          <t>J. NEBRA SANCHEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,64 +2277,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.745</v>
+        <v>-2.8657</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3592</v>
+        <v>-1.2973</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3858</v>
+        <v>-1.5684</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5845</v>
+        <v>-2.2876</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1517</v>
+        <v>0.8012</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4327</v>
+        <v>-3.0887</v>
       </c>
       <c r="J24" t="n">
-        <v>1.042</v>
+        <v>-0.2205</v>
       </c>
       <c r="K24" t="n">
-        <v>0.555</v>
+        <v>1.9355</v>
       </c>
       <c r="L24" t="n">
-        <v>0.487</v>
+        <v>-2.156</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6265</v>
+        <v>-2.0671</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7067</v>
+        <v>-1.1343</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9198</v>
+        <v>-0.9328</v>
       </c>
       <c r="P24" t="n">
+        <v>-0.3968</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-2.9758</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4346</v>
+        <v>-0.1814</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6914</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7432</v>
+        <v>-0.0964</v>
       </c>
       <c r="V24" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0568</v>
+        <v>-3.0049</v>
       </c>
       <c r="E25" t="n">
         <v>-2.4206</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6362</v>
+        <v>-0.5843</v>
       </c>
       <c r="G25" t="n">
         <v>-3.4659</v>
@@ -2400,13 +2400,13 @@
         <v>0.1984</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4767</v>
+        <v>0.5286</v>
       </c>
       <c r="T25" t="n">
         <v>0.1191</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3576</v>
+        <v>0.4095</v>
       </c>
       <c r="V25" t="n">
         <v>-0.266</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.3743</v>
+        <v>-3.3199</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4503</v>
+        <v>-2.7564</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.924</v>
+        <v>-0.5635</v>
       </c>
       <c r="G26" t="n">
         <v>-2.2515</v>
@@ -2478,13 +2478,13 @@
         <v>0.5952</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6031</v>
+        <v>0.6575</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7993</v>
+        <v>0.4932</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1961</v>
+        <v>0.1643</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3373</v>
@@ -2511,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.3732</v>
+        <v>-6.1095</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.3922</v>
+        <v>-5.2085</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.981</v>
+        <v>-0.9011</v>
       </c>
       <c r="G27" t="n">
         <v>-1.7828</v>
@@ -2556,13 +2556,13 @@
         <v>1.5871</v>
       </c>
       <c r="S27" t="n">
-        <v>0.9886</v>
+        <v>0.2523</v>
       </c>
       <c r="T27" t="n">
-        <v>0.9807</v>
+        <v>0.1645</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0078</v>
+        <v>0.0878</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2065</v>
@@ -2589,13 +2589,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-16.3094</v>
+        <v>-14.949</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.610699999999999</v>
+        <v>-7.6107</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.6988</v>
+        <v>-7.3383</v>
       </c>
       <c r="G28" t="n">
         <v>-6.0489</v>
@@ -2607,7 +2607,7 @@
         <v>-6.704499999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>5.0265</v>
+        <v>5.026499999999999</v>
       </c>
       <c r="K28" t="n">
         <v>7.164600000000002</v>
@@ -2634,13 +2634,13 @@
         <v>11.9032</v>
       </c>
       <c r="S28" t="n">
-        <v>0.05669999999999986</v>
+        <v>1.417</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4826999999999997</v>
+        <v>0.4827000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.4259000000000001</v>
+        <v>0.9344</v>
       </c>
       <c r="V28" t="n">
         <v>-5.3579</v>
